--- a/docs/Requirements/Stakeholder Register.xlsx
+++ b/docs/Requirements/Stakeholder Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c906530d9ff38bc/Desktop/SEN381/Ticketing-System/docs/Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA4E1E93-64A8-46FA-98DB-44CEA51307FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{DA4E1E93-64A8-46FA-98DB-44CEA51307FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{546B92D0-B2B8-4A0E-8E11-01D101092E0C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{847158FE-7534-471F-B85A-8BA535CE1FB8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="75">
   <si>
     <t>Stakeholder Register</t>
   </si>
@@ -387,12 +387,30 @@
   <si>
     <t>Takeaway:  every stakeholder identified holds either power or a stake — nobody is safely ignorable.</t>
   </si>
+  <si>
+    <t>STK-010</t>
+  </si>
+  <si>
+    <t>Lecturer/Client proxy (Michael)</t>
+  </si>
+  <si>
+    <t>STK-010 . Lecturer/Client proxy (Michael)</t>
+  </si>
+  <si>
+    <t>evidence of controlled engineering, not just working software.</t>
+  </si>
+  <si>
+    <t>verbal instruction in sessions, captured in team notes.</t>
+  </si>
+  <si>
+    <t>Primary Stakeholder</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -494,8 +512,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -544,6 +568,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="19">
     <border>
@@ -763,66 +793,122 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -833,65 +919,55 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1288,33 +1364,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{624916E6-0655-4B20-ADAE-73FAE961E65C}">
-  <dimension ref="A1:R40"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.21875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="33.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="73.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="68" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.88671875" style="3"/>
-    <col min="12" max="12" width="10.5546875" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="2.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="73.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="68" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.88671875" style="1"/>
+    <col min="12" max="12" width="10.5546875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1"/>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
       <c r="I1"/>
       <c r="J1"/>
       <c r="K1"/>
@@ -1328,15 +1404,15 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2"/>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
       <c r="I2"/>
       <c r="J2"/>
       <c r="K2"/>
@@ -1370,25 +1446,25 @@
     </row>
     <row r="4" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4"/>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I4"/>
@@ -1404,25 +1480,25 @@
     </row>
     <row r="5" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5"/>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="55" t="s">
         <v>15</v>
       </c>
       <c r="I5"/>
@@ -1438,25 +1514,25 @@
     </row>
     <row r="6" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6"/>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="56" t="s">
         <v>21</v>
       </c>
       <c r="I6"/>
@@ -1472,25 +1548,25 @@
     </row>
     <row r="7" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7"/>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="57" t="s">
         <v>26</v>
       </c>
       <c r="I7"/>
@@ -1506,25 +1582,25 @@
     </row>
     <row r="8" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8"/>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="56" t="s">
         <v>31</v>
       </c>
       <c r="I8"/>
@@ -1540,25 +1616,25 @@
     </row>
     <row r="9" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9"/>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="57" t="s">
         <v>36</v>
       </c>
       <c r="I9"/>
@@ -1574,25 +1650,25 @@
     </row>
     <row r="10" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10"/>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="56" t="s">
         <v>41</v>
       </c>
       <c r="I10"/>
@@ -1608,25 +1684,25 @@
     </row>
     <row r="11" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11"/>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="57" t="s">
         <v>46</v>
       </c>
       <c r="I11"/>
@@ -1642,25 +1718,25 @@
     </row>
     <row r="12" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12"/>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="56" t="s">
         <v>51</v>
       </c>
       <c r="I12"/>
@@ -1676,25 +1752,25 @@
     </row>
     <row r="13" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13"/>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="57" t="s">
         <v>56</v>
       </c>
       <c r="I13"/>
@@ -1708,15 +1784,29 @@
       <c r="Q13"/>
       <c r="R13"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14"/>
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
+      <c r="B14" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="58" t="s">
+        <v>73</v>
+      </c>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1728,17 +1818,15 @@
       <c r="Q14"/>
       <c r="R14"/>
     </row>
-    <row r="15" spans="1:18" ht="18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15"/>
-      <c r="B15" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="48"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1752,15 +1840,13 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16"/>
-      <c r="B16" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1772,15 +1858,17 @@
       <c r="Q16"/>
       <c r="R16"/>
     </row>
-    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="18" x14ac:dyDescent="0.3">
       <c r="A17"/>
-      <c r="B17"/>
-      <c r="C17"/>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
+      <c r="B17" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1792,21 +1880,17 @@
       <c r="Q17"/>
       <c r="R17"/>
     </row>
-    <row r="18" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18"/>
-      <c r="B18" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18" s="23"/>
-      <c r="H18" s="24"/>
+      <c r="B18" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1818,21 +1902,15 @@
       <c r="Q18"/>
       <c r="R18"/>
     </row>
-    <row r="19" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="17" t="str">
-        <f>$B$10&amp;"   ·   "&amp;$C$10</f>
-        <v>STK-006   ·   Campus security officer</v>
-      </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="27" t="str">
-        <f>$B$6&amp;"   ·   "&amp;$C$6</f>
-        <v>STK-002   ·   Facilities / maintenance technician</v>
-      </c>
-      <c r="G19" s="17"/>
-      <c r="H19" s="26"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1844,21 +1922,21 @@
       <c r="Q19"/>
       <c r="R19"/>
     </row>
-    <row r="20" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="17" t="str">
-        <f>$B$11&amp;"   ·   "&amp;$C$11</f>
-        <v>STK-007   ·   System administrator</v>
-      </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="27" t="str">
-        <f>$B$7&amp;"   ·   "&amp;$C$7</f>
-        <v>STK-003   ·   IT support technician</v>
-      </c>
-      <c r="G20" s="17"/>
-      <c r="H20" s="26"/>
+      <c r="B20" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="33"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="45"/>
+      <c r="H20" s="46"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1872,18 +1950,18 @@
     </row>
     <row r="21" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="17" t="str">
-        <f>$B$12&amp;"   ·   "&amp;$C$12</f>
-        <v>STK-008   ·   Campus executive sponsor</v>
-      </c>
-      <c r="D21" s="17"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="25" t="str">
+        <f>$B$10&amp;"   ·   "&amp;$C$10</f>
+        <v>STK-006   ·   Campus security officer</v>
+      </c>
+      <c r="D21" s="25"/>
       <c r="E21" s="26"/>
-      <c r="F21" s="27" t="str">
-        <f>$B$8&amp;"   ·   "&amp;$C$8</f>
-        <v>STK-004   ·   Service desk coordinator</v>
-      </c>
-      <c r="G21" s="17"/>
+      <c r="F21" s="24" t="str">
+        <f>$B$6&amp;"   ·   "&amp;$C$6</f>
+        <v>STK-002   ·   Facilities / maintenance technician</v>
+      </c>
+      <c r="G21" s="25"/>
       <c r="H21" s="26"/>
       <c r="I21"/>
       <c r="J21"/>
@@ -1896,21 +1974,21 @@
       <c r="Q21"/>
       <c r="R21"/>
     </row>
-    <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="29" t="str">
-        <f>$B$13&amp;"   ·   "&amp;$C$13</f>
-        <v>STK-009   ·   Information officer / POPIA compliance</v>
-      </c>
-      <c r="D22" s="29"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="31" t="str">
-        <f>$B$9&amp;"   ·   "&amp;$C$9</f>
-        <v>STK-005   ·   Operations manager</v>
-      </c>
-      <c r="G22" s="29"/>
-      <c r="H22" s="30"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="25" t="str">
+        <f>$B$11&amp;"   ·   "&amp;$C$11</f>
+        <v>STK-007   ·   System administrator</v>
+      </c>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="24" t="str">
+        <f>$B$7&amp;"   ·   "&amp;$C$7</f>
+        <v>STK-003   ·   IT support technician</v>
+      </c>
+      <c r="G22" s="25"/>
+      <c r="H22" s="26"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -1922,15 +2000,21 @@
       <c r="Q22"/>
       <c r="R22"/>
     </row>
-    <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23"/>
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="25" t="str">
+        <f>$B$12&amp;"   ·   "&amp;$C$12</f>
+        <v>STK-008   ·   Campus executive sponsor</v>
+      </c>
+      <c r="D23" s="25"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="24" t="str">
+        <f>$B$8&amp;"   ·   "&amp;$C$8</f>
+        <v>STK-004   ·   Service desk coordinator</v>
+      </c>
+      <c r="G23" s="25"/>
+      <c r="H23" s="26"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -1942,21 +2026,21 @@
       <c r="Q23"/>
       <c r="R23"/>
     </row>
-    <row r="24" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24"/>
-      <c r="B24" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" s="33"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="G24" s="20"/>
-      <c r="H24" s="21"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="24" t="str">
+        <f>$B$13&amp;"   ·   "&amp;$C$13</f>
+        <v>STK-009   ·   Information officer / POPIA compliance</v>
+      </c>
+      <c r="D24" s="51"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="24" t="str">
+        <f>$B$9&amp;"   ·   "&amp;$C$9</f>
+        <v>STK-005   ·   Operations manager</v>
+      </c>
+      <c r="G24" s="51"/>
+      <c r="H24" s="26"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -1968,20 +2052,17 @@
       <c r="Q24"/>
       <c r="R24"/>
     </row>
-    <row r="25" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="27" t="str">
-        <f>$B$5&amp;"   ·   "&amp;$C$5</f>
-        <v>STK-001   ·   Student / staff requester</v>
-      </c>
-      <c r="G25" s="17"/>
-      <c r="H25" s="26"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="60" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="61"/>
+      <c r="H25" s="62"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -1995,13 +2076,13 @@
     </row>
     <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="43"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2013,19 +2094,21 @@
       <c r="Q26"/>
       <c r="R26"/>
     </row>
-    <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27"/>
-      <c r="B27"/>
-      <c r="C27" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="45"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="G27" s="45"/>
-      <c r="H27" s="46"/>
+      <c r="B27" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="30"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="G27" s="33"/>
+      <c r="H27" s="34"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2037,15 +2120,20 @@
       <c r="Q27"/>
       <c r="R27"/>
     </row>
-    <row r="28" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28"/>
-      <c r="B28"/>
-      <c r="C28"/>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="25"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="24" t="str">
+        <f>$B$5&amp;"   ·   "&amp;$C$5</f>
+        <v>STK-001   ·   Student / staff requester</v>
+      </c>
+      <c r="G28" s="25"/>
+      <c r="H28" s="26"/>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2059,15 +2147,13 @@
     </row>
     <row r="29" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29"/>
-      <c r="B29" s="47" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="49"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="17"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2079,15 +2165,19 @@
       <c r="Q29"/>
       <c r="R29"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30"/>
       <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
+      <c r="C30" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="19"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="G30" s="19"/>
+      <c r="H30" s="20"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2099,7 +2189,7 @@
       <c r="Q30"/>
       <c r="R30"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31"/>
       <c r="B31"/>
       <c r="C31"/>
@@ -2119,15 +2209,17 @@
       <c r="Q31"/>
       <c r="R31"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32"/>
-      <c r="B32"/>
-      <c r="C32"/>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
-      <c r="G32"/>
-      <c r="H32"/>
+      <c r="B32" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="23"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2299,33 +2391,96 @@
       <c r="Q40"/>
       <c r="R40"/>
     </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
+      <c r="Q41"/>
+      <c r="R41"/>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A42"/>
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+      <c r="P42"/>
+      <c r="Q42"/>
+      <c r="R42"/>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A43"/>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
+      <c r="P43"/>
+      <c r="Q43"/>
+      <c r="R43"/>
+    </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="B29:H29"/>
+  <mergeCells count="25">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="C20:E20"/>
     <mergeCell ref="F20:H20"/>
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="F21:H21"/>
     <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="B32:H32"/>
     <mergeCell ref="F22:H22"/>
-    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F23:H23"/>
     <mergeCell ref="C24:E24"/>
     <mergeCell ref="F24:H24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B18:B22"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="F28:H28"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:G13">
+  <phoneticPr fontId="13" type="noConversion"/>
+  <conditionalFormatting sqref="F5:G15">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",F5)))</formula>
     </cfRule>
